--- a/aq_files/0616.xlsx
+++ b/aq_files/0616.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,856 +413,508 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Q#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Options (if MCQ)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Indexing in arrays starts from:</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>What is the first step when a producer sends a message?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>A) Write to disk B) Get partition assignment C) Serialize the record D) Wait for acknowledgment</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Depends</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Slicing returns:</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Single value</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Subset of array</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sorted array</t>
+          <t>A producer has acks=all and min.insync.replicas=2. The topic has replication factor 3. How many replicas must acknowledge before the write is considered successful?</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>reshape() changes:</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Values</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shape</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Type</t>
+          <t>What is the producer setting that controls how many replicas must acknowledge a write?</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flatten() converts array to:</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2D</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3D</t>
+          <t>What happens when a consumer commits an offset?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1D</t>
+          <t>A) Message is deleted B) Kafka records consumer's position C) Consumer rebalances D) Message is replayed</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>np.zeros() creates:</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ones</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zeros</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Random</t>
+          <t>A consumer group loses a member. What process is triggered?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>np.ones() creates:</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zeros</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ones</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Random</t>
+          <t>What is the maximum message size default in Kafka?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>np.arange() generates:</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sequence</t>
+          <t>How does Kafka guarantee message ordering?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sorted</t>
+          <t>A) Across all partitions B) Within a partition only C) Within a topic only D) No ordering guarantee</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>np.random generates:</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sequence</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Random values</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sorted values</t>
+          <t>A producer with idempotence enabled sends the same message twice due to network retry. Will duplicate messages appear?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>axis=0 refers to:</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Row-wise</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Column-wise</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Total</t>
+          <t>What protocol does Kafka use for replication?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>axis=1 refers to:</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Column-wise</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Row-wise</t>
+          <t>When a consumer reads messages, what is the poll() method responsible for?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>A) Sending messages B) Fetching messages C) Committing offsets D) Closing connection</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Concatenate means:</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Join arrays</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Delete</t>
+          <t>What is the default retention period for messages in Kafka?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Split means:</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Divide arrays</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sort</t>
+          <t>A topic has cleanup.policy=compact. What happens to messages with the same key?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sum along axis=0 gives:</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Row sum</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Column sum</t>
+          <t>What is the purpose of the consumer group coordinator?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>A) Store messages B) Manage group membership and offset commits C) Produce messages D) Monitor brokers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sum along axis=1 gives:</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Column sum</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Row sum</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Total</t>
+          <t>What setting controls the maximum time a consumer can be inactive before being considered dead?</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Define slicing.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Extract subset of array</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>One Word</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>In Kafka workflow, what triggers log rolling?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A) Time-based only B) Size-based only C) Either time or size threshold D) Manual trigger</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>What is reshape?</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Change array dimensions</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>One Word</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>A producer fails to send a message after max retries. What happens?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>You need numbers from 0 to 49 quickly. Which function?</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>zeros</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ones</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>arange</t>
+          <t>What is the process of moving partition leadership from one broker to another called?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>random</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Convert 2D array into 1D for ML input. Which operation?</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>reshape</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>flatten</t>
+          <t>What does the Kafka consumer "auto.offset.reset" setting do?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>split</t>
+          <t>A) Resets consumer group B) Determines behavior when no committed offset exists C) Automatically deletes offsets D) Resets broker connection</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>concat</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Combine two datasets row-wise. Which function?</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>split</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>concatenate</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>reshape</t>
+          <t>What is the value of auto.offset.reset that reads from the earliest available offset?</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Access element at index 2. What index?</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>A topic has retention.ms=86400000 and retention.bytes=1073741824. Which condition triggers deletion first?</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
